--- a/data_raw/gdp.xlsx
+++ b/data_raw/gdp.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>地区生产总值(亿元)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2302 +420,2458 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地区生产总值(亿元)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>10825.4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>13179.8</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>14877.1</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>16181.4</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>18319.6</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>20406.1</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>21774.9</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>23809.4</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>25964.5</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>27821.6</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>30963.9</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>34378.3</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>37769.1</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>40241.2</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>41603.9</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>47059.4</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>48594.5</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>51404.5</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>53759.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>654.3019</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>820.28</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>1020.3488</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1095</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1338.5</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1690.0347</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>2004.1</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>2202.8545</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>2461.4698</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>2631.6398</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>2458.9766</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>2743.8202</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>3099.7659</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>3413</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>3337</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>3691.57</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>3893.22</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>4168</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>4502.16</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>638.4705</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>732.7581</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>846.2811</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>926</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1100.4</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1360.0299</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1563.8</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>1776.2823</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>2000.9389</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>2095.992</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>2264.2318</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>2523.5441</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>2732.9373</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>2837</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>2887</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>3231.29</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>3343.5</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>3487</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>3742.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>8618.9</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>10730.4</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>12167.6</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>13335.7</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>15420.2</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>17653.3</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>19568.3</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>21746</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>23577.5</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>26034.1</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>28438.7</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>31325.9</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>35161.4</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>37767</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>38503.6</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>44350.7</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>45222.4</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>47353.7</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>49670.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>2773.78</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>3283.73</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>3775</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>4230</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>5130.7</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>6145.52</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>7201.6</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>8011.78</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>8820.75</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>9720.77</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>10503.02</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>11715.1</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>12820.4</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>14031</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>14818</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>16356</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>16907.85</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>17421</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>18500.81</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>870.1481</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1069.0099</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1316.2137</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1525</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1800.3</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>2211.4</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>2503.2</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>2803.5444</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>3148.2973</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>3410.0859</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>3703.33</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>4118.8292</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>4026.9053</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>4507</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>4726</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>5120.94</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>5218.35</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>5469</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>5995.36</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1183.8973</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1389.892</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1660.0847</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1838</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>2200.1</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>2688.8724</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>3000.5</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>3336.0265</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>3667.9635</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>4000.014</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>4354.9927</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>5003.1896</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>5274.6716</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>5596</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>5746</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>6650.53</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>7203.5</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>7213</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>7800.37</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1168.0229</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1387.852</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1560.0218</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1737</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>2060.1</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>2539.3132</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>2817.1</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>3018.1565</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>3273.5772</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>3466.0288</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>3784.2662</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>4351.7</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>4791.4131</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>5995</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>6384</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>7033.89</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>7802.66</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>8066</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>8589.01</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1073.76</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1334.6102</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>1664.84</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>2102</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>2701.6</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>3636.6</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>4164.3</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>4672.91</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>5157.9732</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>5660.27</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>6274.3777</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>7213.4476</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>7822.9061</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>9409</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>10046</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>11412.8</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>12013.1</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>12674</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>13507.69</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>900.0845</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1101.1331</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>1316.37</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1644</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1865.7</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>2177.2669</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>2475.6</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>2710.39</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>2894.05</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>3090.52</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>3173.59</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>2743.72</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>2903.5</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>2791</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>2801</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>3121.43</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>3329.1</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>3802</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>4107.08</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2094.0751</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>2436.8044</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>2868.1851</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>3175</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>3664.9</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>4242.1894</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>4550.2</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>5017.0491</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>5340.0715</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>5751.2119</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>6101.6096</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>6355.0487</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>6300.4794</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>5249</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>5184</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>5351.66</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>5490.1</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>5576</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>6016.33</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>2569.6699</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>3130.6789</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>3858.2471</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>4350</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>5158.2</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>6150.6265</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>7002.8</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>7650.7861</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>7655.5761</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>7731.6363</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>6810.1998</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>7363.9182</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>7668.4823</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>7002</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>7030</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>7825.95</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>8430.950000000001</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>8753</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>9516.870000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>3592.5</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>4229.8</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>5278.3</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>5828.6</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>6991.6</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>8240.799999999999</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>9193</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>10075.2</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>10749.2</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>10889.2</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>11487</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>12468.2</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>13411.1</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>14097.2</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>14230.8</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>16093.2</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>16588.5</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>17211.8</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>17931.3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1013.6482</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1254.9447</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1468.0851</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1545</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1778.1</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>2080.1243</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>2311.4</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>2412.8724</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>2531.0917</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>2735.3442</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>2955.6045</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>3382.1819</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>3884.4778</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>4029</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>4153</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>5121.61</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>5571.17</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>5574</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>5418.87</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>2874.4435</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>3435.0042</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>3964.0472</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>4329</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>5163</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>6059.2409</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>6582.2</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>7128.8672</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>7610.2816</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>8003.6103</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>8686.491099999999</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>9842.1</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>10745.4632</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>11985</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>12409</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>14594.92</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>15704.3</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>16453</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>18147.7</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>6073.8277</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>7109.1814</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>8215.8151</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>9138</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>10748.3</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>12423.439</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>13551.2</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>15420.1434</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>16706.8719</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>18100.4136</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>19547.442</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>21503.1516</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>22859.3471</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>23629</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>25019</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>28231.97</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>28839</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>30356</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>31032.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>2750.4776</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>3324.1677</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>3900.9857</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>4503</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>5551.3</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>6854.5786</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>8138.9</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>9108.8904</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>10056.5926</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>10801.1633</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>12170.2335</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>13889.394</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>15342.7716</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>17013</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>17717</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>19916.98</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>20817.5</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>22075</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>23511.34</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
         <v>121.91</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>142.05</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>163</v>
       </c>
-      <c r="G19">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>222.4192</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>260.1</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>304.87</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>347.45</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>376.73</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>424.95</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>479.25</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>540.78</v>
       </c>
-      <c r="O19">
+      <c r="O19" t="n">
         <v>618</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="n">
         <v>678</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" t="n">
         <v>741.84</v>
       </c>
-      <c r="R19">
+      <c r="R19" t="n">
         <v>747.5700000000001</v>
       </c>
-      <c r="S19">
+      <c r="S19" t="n">
         <v>835</v>
       </c>
-      <c r="T19">
+      <c r="T19" t="n">
         <v>990.04</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>1207.2855</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1405.0473</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>1511.6795</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>1809</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>2120.4</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>2509.5813</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>3011.1</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>3415.3115</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>3712.9943</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>3968.0051</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>4300.078</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>4857.6426</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>5206.8979</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>6476</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>6734</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>7222.5</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>7541.37</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>7865</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>8275.219999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>3441.5068</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>4100.1722</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>4781.1649</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>5088</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>5949.2</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>7019.0579</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>7802</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>8343.5193</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>9206.1633</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>10050.2079</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>11313.7223</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>12603.3629</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>13509.1508</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>15373</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>16106</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>18109.42</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>18753.07</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>20059</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>21860.32</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>2590.7569</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>3141.9048</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>3960.0819</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>4621</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>5565.9</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>6762.2</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>8003.8</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>9051.27</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>10069.48</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>10905.6</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>11912.61</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>13410.34</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>14847.29</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>16223</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>15616</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>17716.76</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>18866.43</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>20012</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>21106.23</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>2519.6338</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>3221.1508</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>3860.4745</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>4269</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>5017.5</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>5915.7142</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>6602.6</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>7158.5745</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>7098.7051</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>7272.3051</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>5546.4498</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>5864.9653</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>6292.3981</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>6470</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>6572</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>7249</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>7695.8</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>8122</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>9027.139999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>2185.0856</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>2562.8135</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>3017.4243</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>3351</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>3910.5</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>4406.29</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>4803.7</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>5230.1948</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>5770.5966</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>6100.232</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>6536.1165</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>7201.96</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>7856.56</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>9443</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>10141</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>11432.22</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>12027.46</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>12757</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>13527.55</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>350.1246</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>393.6858</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>443.1808</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>490</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>595.1</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>713.3</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>818.8</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>904.6355</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>1091.7021</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>1161.9648</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>1257.6653</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>1390.5779</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>1510.513</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>1672</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>1792</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>2057.06</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>2134.77</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>2358</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>2470.63</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>5813.5624</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>6801.5706</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>7806.5387</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>8201</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>9581.5</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>11505.5298</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>12950.1</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>14500.2302</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>16001.8207</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>17502.8634</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>19492.6012</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>22490.0586</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>24221.9771</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>26927</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>27670</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>30664.85</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>32387.68</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>34606</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>36801.87</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>2026.632</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>2360.723</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>2838.3712</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>3001</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>3401</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>4082.6833</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>4500.2</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>4863.6583</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>5170.2653</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>5440.5988</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>5927.7293</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>6460.8848</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>6082.618</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>5810</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>5935</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>6490.3</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>7100.64</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>7534</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>8203.440000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>1664.0515</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1974.5818</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>2284.1602</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>2604</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>3123.4</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>3736.3796</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>4218.3</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>4678.4951</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>5169.1647</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>5618.0844</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>6197.6395</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>7103.4</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>7856.8123</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>9392</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>10020</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>11324.48</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>12308.23</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>12928</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>14236.76</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>281.6093</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>342.4581</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>422.1885</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>501</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>628.3</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>770.7043</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>851.1</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>978.5314</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>1065.7811</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>1131.6193</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>1248.1677</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>1284.9081</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>1286.4137</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>1328</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>1373</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>1548.79</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>1644.35</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>1801</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>1862.09</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>1473.68</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1763.73</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>2190.04</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>2724</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>3241.5</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>3864.21</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>4366.1</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>4884.13</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>5492.64</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>5801.2</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>6257.18</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>7469.848</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>8349.860000000001</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>9321</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>10020</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>10688.28</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>11486.51</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>12011</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>13317.78</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>602.8845</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>693.717</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>811.0521</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>972</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>1121.8</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>1383.0724</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>1700.3</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>2085.4234</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>2497.2691</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>2891.16</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>3157.7001</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>3537.9637</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>3798.4538</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>4040</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>4312</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>4711.03</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>4921.17</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>5155</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>5777.41</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>2013.4777</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>2486.747</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>3003.9925</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>3308</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>4040.9</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>4979.8455</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>5549.8</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>6201.9</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>6776.989</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>7311.521</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>8113.9666</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>9130.200000000001</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>10143.3173</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>11590</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>12004</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>12691.02</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>12934.7</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>13618</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>14532.07</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>3949</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>4837.5</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>5978.8</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>6744.1</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>8186.5</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>10314.1</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>11797.8</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>13275.8</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>14911.7</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>16305.9</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>18271.1</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>20260.8</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>21866.8</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>23689.6</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>25158.1</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>28092.5</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>28771.8</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>30614.3</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>32046.7</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>335.2918</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>408.6009</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>514.1138</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>578</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>769.4</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>986.6761</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>1150.9</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>1289.0199</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>1388.6244</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>1493.859</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>1617.7071</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>1803.2581</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>1901.4824</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>1897</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>1964</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>2262.95</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>2535.63</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>2686</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>2939.53</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>1741.1922</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>2089.0859</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>2561.8985</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>2849</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>3329</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>4003.0775</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>4456.6</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>5003.1808</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>5342.4262</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>5530.0345</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>5986.42</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>6530.0308</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>7175.7117</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>5904</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>6638</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>7103.1</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>6744.56</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>7002</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>7632.19</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>1798.9572</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>2190.2548</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>3000.9795</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>3745</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>4547.1</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>5619.3285</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>6399.9</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>7153.1346</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>7824.8074</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>8510.132799999999</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>9356.908799999999</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>10535.5072</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>11003.4116</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>11574</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>12143</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>13270.7</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>13966.11</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>14332</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>15268.78</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>3206.58</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>3786.5156</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>4436.18</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>4854</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>5666.2</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>6615.6</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>7302.1</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>8006.6</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>8692.1</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>9300.07</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>10011.29</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>11037.28</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>12001.52</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>11741</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>12401</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>14136</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>14920.75</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>15760</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>16719.46</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data_raw/gdp.xlsx
+++ b/data_raw/gdp.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>地区生产总值(亿元)</t>
+          <t>地区生产总值（当年价格）(亿元)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -527,11 +527,6 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -598,7 +593,6 @@
       <c r="T2" t="n">
         <v>53759.5</v>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -663,7 +657,6 @@
       <c r="T3" t="n">
         <v>4502.16</v>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -728,7 +721,6 @@
       <c r="T4" t="n">
         <v>3742.25</v>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -793,7 +785,6 @@
       <c r="T5" t="n">
         <v>49670.2</v>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -858,7 +849,6 @@
       <c r="T6" t="n">
         <v>18500.81</v>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -923,7 +913,6 @@
       <c r="T7" t="n">
         <v>5995.36</v>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -988,7 +977,6 @@
       <c r="T8" t="n">
         <v>7800.37</v>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1053,7 +1041,6 @@
       <c r="T9" t="n">
         <v>8589.01</v>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1118,7 +1105,6 @@
       <c r="T10" t="n">
         <v>13507.69</v>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1183,7 +1169,6 @@
       <c r="T11" t="n">
         <v>4107.08</v>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1248,7 +1233,6 @@
       <c r="T12" t="n">
         <v>6016.33</v>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1313,7 +1297,6 @@
       <c r="T13" t="n">
         <v>9516.870000000001</v>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1378,7 +1361,6 @@
       <c r="T14" t="n">
         <v>17931.3</v>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1443,7 +1425,6 @@
       <c r="T15" t="n">
         <v>5418.87</v>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1508,7 +1489,6 @@
       <c r="T16" t="n">
         <v>18147.7</v>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1573,7 +1553,6 @@
       <c r="T17" t="n">
         <v>31032.5</v>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1638,7 +1617,6 @@
       <c r="T18" t="n">
         <v>23511.34</v>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1699,7 +1677,6 @@
       <c r="T19" t="n">
         <v>990.04</v>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1764,7 +1741,6 @@
       <c r="T20" t="n">
         <v>8275.219999999999</v>
       </c>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1829,7 +1805,6 @@
       <c r="T21" t="n">
         <v>21860.32</v>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -1894,7 +1869,6 @@
       <c r="T22" t="n">
         <v>21106.23</v>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1959,7 +1933,6 @@
       <c r="T23" t="n">
         <v>9027.139999999999</v>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2024,7 +1997,6 @@
       <c r="T24" t="n">
         <v>13527.55</v>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2089,7 +2061,6 @@
       <c r="T25" t="n">
         <v>2470.63</v>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2154,7 +2125,6 @@
       <c r="T26" t="n">
         <v>36801.87</v>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2219,7 +2189,6 @@
       <c r="T27" t="n">
         <v>8203.440000000001</v>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2284,7 +2253,6 @@
       <c r="T28" t="n">
         <v>14236.76</v>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2349,7 +2317,6 @@
       <c r="T29" t="n">
         <v>1862.09</v>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2414,7 +2381,6 @@
       <c r="T30" t="n">
         <v>13317.78</v>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2479,7 +2445,6 @@
       <c r="T31" t="n">
         <v>5777.41</v>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2544,7 +2509,6 @@
       <c r="T32" t="n">
         <v>14532.07</v>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2609,7 +2573,6 @@
       <c r="T33" t="n">
         <v>32046.7</v>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -2674,7 +2637,6 @@
       <c r="T34" t="n">
         <v>2939.53</v>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2739,7 +2701,6 @@
       <c r="T35" t="n">
         <v>7632.19</v>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -2804,7 +2765,6 @@
       <c r="T36" t="n">
         <v>15268.78</v>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2869,7 +2829,6 @@
       <c r="T37" t="n">
         <v>16719.46</v>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
